--- a/API-Excel/API_Analysis_HEADER_NAV.xlsx
+++ b/API-Excel/API_Analysis_HEADER_NAV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangoctai/StudySpace/SOA.2026/Minh Giang Pharmacy/API-Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B362AA7-5EBD-2644-8C15-B2670F65EBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8310D367-3AED-E842-B4E6-9F1385EFFB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="500" windowWidth="32440" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -749,7 +749,7 @@
     <col min="4" max="4" width="108.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="83.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="101.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" customWidth="1"/>
     <col min="8" max="8" width="127.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
